--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>订单类型</t>
   </si>
@@ -37,25 +37,61 @@
     <t>对账状态</t>
   </si>
   <si>
+    <t>支付状态</t>
+  </si>
+  <si>
+    <t>核算状态</t>
+  </si>
+  <si>
     <t>物流渠道</t>
   </si>
   <si>
+    <t>物流运单号</t>
+  </si>
+  <si>
     <t>物流跟踪单号</t>
   </si>
   <si>
     <t>运输状态</t>
   </si>
   <si>
+    <t>实重</t>
+  </si>
+  <si>
+    <t>体积</t>
+  </si>
+  <si>
+    <t>体积重</t>
+  </si>
+  <si>
+    <t>计费重</t>
+  </si>
+  <si>
+    <t>预估运费</t>
+  </si>
+  <si>
+    <t>预估关税费用</t>
+  </si>
+  <si>
+    <t>预估其他费用</t>
+  </si>
+  <si>
     <t>计费重[物流商]</t>
   </si>
   <si>
-    <t>实际运费</t>
-  </si>
-  <si>
-    <t>实际报关费</t>
-  </si>
-  <si>
-    <t>实际其他费用</t>
+    <t>实际运费[总]</t>
+  </si>
+  <si>
+    <t>实际关税费用[总]</t>
+  </si>
+  <si>
+    <t>实际可抵扣税金[总]</t>
+  </si>
+  <si>
+    <t>实际其他费用[总]</t>
+  </si>
+  <si>
+    <t>运费差异</t>
   </si>
   <si>
     <t>平台</t>
@@ -64,9 +100,6 @@
     <t>店铺/客户</t>
   </si>
   <si>
-    <t>店铺负责人</t>
-  </si>
-  <si>
     <t>平台单号</t>
   </si>
   <si>
@@ -85,6 +118,15 @@
     <t>发货时间</t>
   </si>
   <si>
+    <t>计费规则</t>
+  </si>
+  <si>
+    <t>账单确认时间</t>
+  </si>
+  <si>
+    <t>付款/退款时间</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -94,15 +136,45 @@
     <t>{.reconciliationStatusName}</t>
   </si>
   <si>
+    <t>{.payStatusName}</t>
+  </si>
+  <si>
+    <t>{.checkStatusName}</t>
+  </si>
+  <si>
     <t>{.channelName}</t>
   </si>
   <si>
+    <t>{.transportNo}</t>
+  </si>
+  <si>
     <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.transportStatusName}</t>
   </si>
   <si>
+    <t>{.actualWeight}</t>
+  </si>
+  <si>
+    <t>{.volume}</t>
+  </si>
+  <si>
+    <t>{.volumeWeight}</t>
+  </si>
+  <si>
+    <t>{.billingWeight}</t>
+  </si>
+  <si>
+    <t>{.estimatedShippingCost}</t>
+  </si>
+  <si>
+    <t>{.estimatedDeclareCost}</t>
+  </si>
+  <si>
+    <t>{.estimatedOtherCost}</t>
+  </si>
+  <si>
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
@@ -112,18 +184,21 @@
     <t>{.actualDeclareCost}</t>
   </si>
   <si>
+    <t>{.actualDeductibleTax}</t>
+  </si>
+  <si>
     <t>{.actualOtherCost}</t>
   </si>
   <si>
+    <t>{.diffShippingCost}</t>
+  </si>
+  <si>
     <t>{.salesPlatform}</t>
   </si>
   <si>
     <t>{.customerName}</t>
   </si>
   <si>
-    <t>{.shopChargeName}</t>
-  </si>
-  <si>
     <t>{.platformCode}</t>
   </si>
   <si>
@@ -140,6 +215,15 @@
   </si>
   <si>
     <t>{.deliveryTime}</t>
+  </si>
+  <si>
+    <t>{.feeRuleName}</t>
+  </si>
+  <si>
+    <t>{.confirmTime}</t>
+  </si>
+  <si>
+    <t>{.payTime}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1073,26 +1157,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
     <col min="2" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="13.625" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="17.125" customWidth="1"/>
-    <col min="7" max="9" width="20.75" customWidth="1"/>
-    <col min="10" max="10" width="16.5" customWidth="1"/>
-    <col min="11" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="18.25" customWidth="1"/>
-    <col min="14" max="14" width="15.75" customWidth="1"/>
-    <col min="15" max="15" width="13.875" customWidth="1"/>
-    <col min="16" max="16" width="13.75" customWidth="1"/>
-    <col min="17" max="18" width="13.125" customWidth="1"/>
+    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="4" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="11" width="16.375" customWidth="1"/>
+    <col min="12" max="12" width="12.375" customWidth="1"/>
+    <col min="13" max="13" width="14.25" customWidth="1"/>
+    <col min="14" max="14" width="21.625" customWidth="1"/>
+    <col min="15" max="16" width="17.125" customWidth="1"/>
+    <col min="17" max="20" width="20.75" customWidth="1"/>
+    <col min="21" max="21" width="16.75" customWidth="1"/>
+    <col min="22" max="22" width="16.5" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
+    <col min="24" max="24" width="18.25" customWidth="1"/>
+    <col min="25" max="25" width="15.75" customWidth="1"/>
+    <col min="26" max="26" width="13.875" customWidth="1"/>
+    <col min="27" max="27" width="13.75" customWidth="1"/>
+    <col min="28" max="29" width="13.125" customWidth="1"/>
+    <col min="30" max="30" width="8.875" customWidth="1"/>
+    <col min="31" max="31" width="12.875" customWidth="1"/>
+    <col min="32" max="32" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1150,64 +1245,148 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>51</v>
+      </c>
+      <c r="T2" t="s">
+        <v>52</v>
+      </c>
+      <c r="U2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V2" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>订单类型</t>
   </si>
@@ -64,18 +64,6 @@
     <t>体积重</t>
   </si>
   <si>
-    <t>计费重</t>
-  </si>
-  <si>
-    <t>预估运费</t>
-  </si>
-  <si>
-    <t>预估关税费用</t>
-  </si>
-  <si>
-    <t>预估其他费用</t>
-  </si>
-  <si>
     <t>计费重[物流商]</t>
   </si>
   <si>
@@ -91,9 +79,6 @@
     <t>实际其他费用[总]</t>
   </si>
   <si>
-    <t>运费差异</t>
-  </si>
-  <si>
     <t>平台</t>
   </si>
   <si>
@@ -163,18 +148,6 @@
     <t>{.volumeWeight}</t>
   </si>
   <si>
-    <t>{.billingWeight}</t>
-  </si>
-  <si>
-    <t>{.estimatedShippingCost}</t>
-  </si>
-  <si>
-    <t>{.estimatedDeclareCost}</t>
-  </si>
-  <si>
-    <t>{.estimatedOtherCost}</t>
-  </si>
-  <si>
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
@@ -188,9 +161,6 @@
   </si>
   <si>
     <t>{.actualOtherCost}</t>
-  </si>
-  <si>
-    <t>{.diffShippingCost}</t>
   </si>
   <si>
     <t>{.salesPlatform}</t>
@@ -1157,7 +1127,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1169,25 +1139,21 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="13.25" customWidth="1"/>
     <col min="10" max="11" width="16.375" customWidth="1"/>
-    <col min="12" max="12" width="12.375" customWidth="1"/>
-    <col min="13" max="13" width="14.25" customWidth="1"/>
-    <col min="14" max="14" width="21.625" customWidth="1"/>
-    <col min="15" max="16" width="17.125" customWidth="1"/>
-    <col min="17" max="20" width="20.75" customWidth="1"/>
-    <col min="21" max="21" width="16.75" customWidth="1"/>
-    <col min="22" max="22" width="16.5" customWidth="1"/>
-    <col min="23" max="23" width="16" customWidth="1"/>
-    <col min="24" max="24" width="18.25" customWidth="1"/>
-    <col min="25" max="25" width="15.75" customWidth="1"/>
-    <col min="26" max="26" width="13.875" customWidth="1"/>
-    <col min="27" max="27" width="13.75" customWidth="1"/>
-    <col min="28" max="29" width="13.125" customWidth="1"/>
-    <col min="30" max="30" width="8.875" customWidth="1"/>
-    <col min="31" max="31" width="12.875" customWidth="1"/>
-    <col min="32" max="32" width="14" customWidth="1"/>
+    <col min="12" max="12" width="17.125" customWidth="1"/>
+    <col min="13" max="16" width="20.75" customWidth="1"/>
+    <col min="17" max="17" width="16.5" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="18.25" customWidth="1"/>
+    <col min="20" max="20" width="15.75" customWidth="1"/>
+    <col min="21" max="21" width="13.875" customWidth="1"/>
+    <col min="22" max="22" width="13.75" customWidth="1"/>
+    <col min="23" max="24" width="13.125" customWidth="1"/>
+    <col min="25" max="25" width="8.875" customWidth="1"/>
+    <col min="26" max="26" width="12.875" customWidth="1"/>
+    <col min="27" max="27" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1272,121 +1238,91 @@
       <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="C2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="D2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:33">
-      <c r="A2" t="s">
+      <c r="F2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" t="s">
+      <c r="I2" t="s">
         <v>36</v>
       </c>
-      <c r="E2" t="s">
+      <c r="J2" t="s">
         <v>37</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" t="s">
+      <c r="L2" t="s">
         <v>39</v>
       </c>
-      <c r="H2" t="s">
+      <c r="M2" t="s">
         <v>40</v>
       </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>41</v>
       </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>42</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>43</v>
       </c>
-      <c r="L2" t="s">
+      <c r="Q2" t="s">
         <v>44</v>
       </c>
-      <c r="M2" t="s">
+      <c r="R2" t="s">
         <v>45</v>
       </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
         <v>46</v>
       </c>
-      <c r="O2" t="s">
+      <c r="T2" t="s">
         <v>47</v>
       </c>
-      <c r="P2" t="s">
+      <c r="U2" t="s">
         <v>48</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="V2" t="s">
         <v>49</v>
       </c>
-      <c r="R2" t="s">
+      <c r="W2" t="s">
         <v>50</v>
       </c>
-      <c r="S2" t="s">
+      <c r="X2" t="s">
         <v>51</v>
       </c>
-      <c r="T2" t="s">
+      <c r="Y2" t="s">
         <v>52</v>
       </c>
-      <c r="U2" t="s">
+      <c r="Z2" t="s">
         <v>53</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AA2" t="s">
         <v>54</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AB2" t="s">
         <v>55</v>
-      </c>
-      <c r="X2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>订单类型</t>
   </si>
@@ -55,15 +55,6 @@
     <t>运输状态</t>
   </si>
   <si>
-    <t>实重</t>
-  </si>
-  <si>
-    <t>体积</t>
-  </si>
-  <si>
-    <t>体积重</t>
-  </si>
-  <si>
     <t>计费重[物流商]</t>
   </si>
   <si>
@@ -137,15 +128,6 @@
   </si>
   <si>
     <t>{.transportStatusName}</t>
-  </si>
-  <si>
-    <t>{.actualWeight}</t>
-  </si>
-  <si>
-    <t>{.volume}</t>
-  </si>
-  <si>
-    <t>{.volumeWeight}</t>
   </si>
   <si>
     <t>{.billingWeightLogistics}</t>
@@ -1127,7 +1109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1137,23 +1119,21 @@
     <col min="6" max="6" width="15.625" customWidth="1"/>
     <col min="7" max="7" width="13.625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13.25" customWidth="1"/>
-    <col min="10" max="11" width="16.375" customWidth="1"/>
-    <col min="12" max="12" width="17.125" customWidth="1"/>
-    <col min="13" max="16" width="20.75" customWidth="1"/>
-    <col min="17" max="17" width="16.5" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="18.25" customWidth="1"/>
-    <col min="20" max="20" width="15.75" customWidth="1"/>
-    <col min="21" max="21" width="13.875" customWidth="1"/>
-    <col min="22" max="22" width="13.75" customWidth="1"/>
-    <col min="23" max="24" width="13.125" customWidth="1"/>
-    <col min="25" max="25" width="8.875" customWidth="1"/>
-    <col min="26" max="26" width="12.875" customWidth="1"/>
-    <col min="27" max="27" width="14" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="13" width="20.75" customWidth="1"/>
+    <col min="14" max="14" width="16.5" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="18.25" customWidth="1"/>
+    <col min="17" max="17" width="15.75" customWidth="1"/>
+    <col min="18" max="18" width="13.875" customWidth="1"/>
+    <col min="19" max="19" width="13.75" customWidth="1"/>
+    <col min="20" max="21" width="13.125" customWidth="1"/>
+    <col min="22" max="22" width="8.875" customWidth="1"/>
+    <col min="23" max="23" width="12.875" customWidth="1"/>
+    <col min="24" max="24" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1229,100 +1209,82 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>33</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>37</v>
       </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
+      <c r="O2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
         <v>40</v>
       </c>
-      <c r="N2" t="s">
+      <c r="Q2" t="s">
         <v>41</v>
       </c>
-      <c r="O2" t="s">
+      <c r="R2" t="s">
         <v>42</v>
       </c>
-      <c r="P2" t="s">
+      <c r="S2" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="T2" t="s">
         <v>44</v>
       </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>45</v>
       </c>
-      <c r="S2" t="s">
+      <c r="V2" t="s">
         <v>46</v>
       </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
         <v>47</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>48</v>
       </c>
-      <c r="V2" t="s">
+      <c r="Y2" t="s">
         <v>49</v>
-      </c>
-      <c r="W2" t="s">
-        <v>50</v>
-      </c>
-      <c r="X2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
@@ -133,16 +133,16 @@
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
-    <t>{.actualShippingCost}</t>
-  </si>
-  <si>
-    <t>{.actualDeclareCost}</t>
-  </si>
-  <si>
-    <t>{.actualDeductibleTax}</t>
-  </si>
-  <si>
-    <t>{.actualOtherCost}</t>
+    <t>{.actualShippingCostStr}</t>
+  </si>
+  <si>
+    <t>{.actualDeclareCostStr}</t>
+  </si>
+  <si>
+    <t>{.actualDeductibleTaxStr}</t>
+  </si>
+  <si>
+    <t>{.actualOtherCostStr}</t>
   </si>
   <si>
     <t>{.salesPlatform}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>订单类型</t>
   </si>
@@ -43,6 +43,9 @@
     <t>核算状态</t>
   </si>
   <si>
+    <t>物流商</t>
+  </si>
+  <si>
     <t>物流渠道</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
   </si>
   <si>
     <t>{.checkStatusName}</t>
+  </si>
+  <si>
+    <t>{.logisticsSupplierName}</t>
   </si>
   <si>
     <t>{.channelName}</t>
@@ -1109,31 +1115,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
     <col min="2" max="2" width="14.25" customWidth="1"/>
     <col min="3" max="3" width="17.25" customWidth="1"/>
-    <col min="4" max="5" width="14.875" customWidth="1"/>
-    <col min="6" max="6" width="15.625" customWidth="1"/>
-    <col min="7" max="7" width="13.625" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="17.125" customWidth="1"/>
-    <col min="10" max="13" width="20.75" customWidth="1"/>
-    <col min="14" max="14" width="16.5" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="18.25" customWidth="1"/>
-    <col min="17" max="17" width="15.75" customWidth="1"/>
-    <col min="18" max="18" width="13.875" customWidth="1"/>
-    <col min="19" max="19" width="13.75" customWidth="1"/>
-    <col min="20" max="21" width="13.125" customWidth="1"/>
-    <col min="22" max="22" width="8.875" customWidth="1"/>
-    <col min="23" max="23" width="12.875" customWidth="1"/>
-    <col min="24" max="24" width="14" customWidth="1"/>
+    <col min="4" max="6" width="14.875" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="13.625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="17.125" customWidth="1"/>
+    <col min="11" max="14" width="20.75" customWidth="1"/>
+    <col min="15" max="15" width="16.5" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="18.25" customWidth="1"/>
+    <col min="18" max="18" width="15.75" customWidth="1"/>
+    <col min="19" max="19" width="13.875" customWidth="1"/>
+    <col min="20" max="20" width="13.75" customWidth="1"/>
+    <col min="21" max="22" width="13.125" customWidth="1"/>
+    <col min="23" max="23" width="8.875" customWidth="1"/>
+    <col min="24" max="24" width="12.875" customWidth="1"/>
+    <col min="25" max="25" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1209,82 +1215,88 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y2" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>订单类型</t>
   </si>
@@ -61,6 +61,12 @@
     <t>计费重[物流商]</t>
   </si>
   <si>
+    <t>包装尺寸（物流商）</t>
+  </si>
+  <si>
+    <t>实重（物流商）</t>
+  </si>
+  <si>
     <t>实际运费[总]</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>销售单号</t>
   </si>
   <si>
+    <t>发货单号</t>
+  </si>
+  <si>
     <t>出库单号</t>
   </si>
   <si>
@@ -139,6 +148,12 @@
     <t>{.billingWeightLogistics}</t>
   </si>
   <si>
+    <t>{.thirdPackSize}</t>
+  </si>
+  <si>
+    <t>{.thirdActualWeight}</t>
+  </si>
+  <si>
     <t>{.actualShippingCostStr}</t>
   </si>
   <si>
@@ -161,6 +176,9 @@
   </si>
   <si>
     <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.soDeliveryCode}</t>
   </si>
   <si>
     <t>{.outstockCode}</t>
@@ -1115,7 +1133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1126,20 +1144,22 @@
     <col min="8" max="8" width="13.625" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="14" width="20.75" customWidth="1"/>
-    <col min="15" max="15" width="16.5" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="18.25" customWidth="1"/>
-    <col min="18" max="18" width="15.75" customWidth="1"/>
-    <col min="19" max="19" width="13.875" customWidth="1"/>
-    <col min="20" max="20" width="13.75" customWidth="1"/>
-    <col min="21" max="22" width="13.125" customWidth="1"/>
-    <col min="23" max="23" width="8.875" customWidth="1"/>
-    <col min="24" max="24" width="12.875" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="11" max="11" width="19.875" customWidth="1"/>
+    <col min="12" max="12" width="20.25" customWidth="1"/>
+    <col min="13" max="16" width="20.75" customWidth="1"/>
+    <col min="17" max="17" width="16.5" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="18.25" customWidth="1"/>
+    <col min="20" max="21" width="15.75" customWidth="1"/>
+    <col min="22" max="22" width="13.875" customWidth="1"/>
+    <col min="23" max="23" width="13.75" customWidth="1"/>
+    <col min="24" max="25" width="13.125" customWidth="1"/>
+    <col min="26" max="26" width="8.875" customWidth="1"/>
+    <col min="27" max="27" width="12.875" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1218,85 +1238,103 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsLastMileCost.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>订单类型</t>
   </si>
@@ -100,6 +100,18 @@
     <t>目的国家</t>
   </si>
   <si>
+    <t>区域</t>
+  </si>
+  <si>
+    <t>部门</t>
+  </si>
+  <si>
+    <t>军区</t>
+  </si>
+  <si>
+    <t>是否分摊</t>
+  </si>
+  <si>
     <t>下单时间</t>
   </si>
   <si>
@@ -185,6 +197,18 @@
   </si>
   <si>
     <t>{.toCountry}</t>
+  </si>
+  <si>
+    <t>{.regionName}</t>
+  </si>
+  <si>
+    <t>{.deptName}</t>
+  </si>
+  <si>
+    <t>{.partitionName}</t>
+  </si>
+  <si>
+    <t>{.isAllocateRequiredName}</t>
   </si>
   <si>
     <t>{.orderTime}</t>
@@ -1133,7 +1157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1153,13 +1177,16 @@
     <col min="20" max="21" width="15.75" customWidth="1"/>
     <col min="22" max="22" width="13.875" customWidth="1"/>
     <col min="23" max="23" width="13.75" customWidth="1"/>
-    <col min="24" max="25" width="13.125" customWidth="1"/>
-    <col min="26" max="26" width="8.875" customWidth="1"/>
-    <col min="27" max="27" width="12.875" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="24" max="24" width="19" customWidth="1"/>
+    <col min="25" max="25" width="17.875" customWidth="1"/>
+    <col min="26" max="27" width="15.875" customWidth="1"/>
+    <col min="28" max="29" width="13.125" customWidth="1"/>
+    <col min="30" max="30" width="8.875" customWidth="1"/>
+    <col min="31" max="31" width="12.875" customWidth="1"/>
+    <col min="32" max="32" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1247,94 +1274,118 @@
       <c r="AC1" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="S2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="T2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="U2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="V2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="W2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="X2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Y2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Z2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="AA2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AB2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="AC2" t="s">
-        <v>57</v>
+        <v>61</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
